--- a/artfynd/S 1362-2023 artfynd.xlsx
+++ b/artfynd/S 1362-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY104"/>
+  <dimension ref="A1:AZ104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87896051</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87895854</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -989,6 +1004,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87895855</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,6 +1106,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87895856</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1183,6 +1208,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87896080</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1303,6 +1333,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65319226</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1428,6 +1463,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65338259</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1525,6 +1565,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87895997</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1627,6 +1672,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87895999</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1729,6 +1779,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87896027</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1844,6 +1899,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93551742</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1967,6 +2027,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93158679</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2091,6 +2156,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93551981</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2193,6 +2263,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87895862</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2295,6 +2370,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87895863</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2402,6 +2482,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87896171</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2504,6 +2589,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87896172</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2606,6 +2696,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87896173</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2708,6 +2803,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87896174</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2815,6 +2915,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87896186</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2917,6 +3022,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87896192</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3019,6 +3129,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87896194</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3121,6 +3236,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87896195</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3228,6 +3348,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87896202</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3335,6 +3460,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87896203</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3436,6 +3566,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92472085</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3547,6 +3682,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92476228</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3653,6 +3793,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92476232</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3776,6 +3921,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98613283</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3878,6 +4028,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87896162</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3984,6 +4139,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92472026</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4095,6 +4255,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92472027</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4201,6 +4366,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92472028</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4312,6 +4482,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92472038</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4418,6 +4593,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92472039</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4524,6 +4704,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92472040</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4630,6 +4815,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92472041</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4736,6 +4926,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92476216</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4849,6 +5044,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93078373</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4968,6 +5168,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94299761</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5082,6 +5287,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112914254</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5194,6 +5404,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126773102</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5300,6 +5515,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92472127</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5418,6 +5638,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65319135</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5528,6 +5753,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92472155</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5638,6 +5868,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92476248</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5739,6 +5974,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92472217</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5849,6 +6089,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92472050</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5951,6 +6196,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87895775</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6053,6 +6303,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87895776</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6155,6 +6410,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87895782</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6261,6 +6521,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87895783</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6363,6 +6628,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87895784</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6465,6 +6735,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87895785</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6567,6 +6842,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87895787</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6669,6 +6949,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87895788</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6766,6 +7051,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87895789</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6868,6 +7158,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87895790</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6965,6 +7260,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87895791</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7067,6 +7367,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87895792</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7169,6 +7474,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87895793</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7271,6 +7581,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87895794</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7382,6 +7697,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87896140</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7490,6 +7810,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87896142</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7601,6 +7926,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87896143</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7712,6 +8042,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87896145</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7823,6 +8158,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87896154</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7924,6 +8264,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87896244</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8026,6 +8371,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87895797</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8128,6 +8478,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87895798</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8225,6 +8580,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87895799</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8327,6 +8687,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87895800</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8429,6 +8794,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87895801</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8531,6 +8901,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87895802</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8642,6 +9017,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87896158</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8743,6 +9123,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87896159</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8849,6 +9234,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87896047</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8955,6 +9345,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87896048</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9061,6 +9456,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87896049</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9167,6 +9567,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74302442</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9273,6 +9678,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74769910</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9370,6 +9780,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87895946</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9476,6 +9891,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87895922</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9582,6 +10002,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87895923</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9688,6 +10113,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87895924</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9794,6 +10224,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87895925</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9900,6 +10335,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87896217</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10002,6 +10442,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87896218</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10108,6 +10553,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87896219</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10210,6 +10660,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87896220</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10312,6 +10767,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87896221</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10418,6 +10878,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92472116</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10528,6 +10993,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92476239</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10638,6 +11108,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92476240</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10748,6 +11223,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92476241</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10854,6 +11334,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87895947</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10960,6 +11445,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74479075</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11062,6 +11552,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87896076</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11168,6 +11663,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87896240</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11274,6 +11774,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87896241</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11387,6 +11892,11 @@
       <c r="AY102" t="inlineStr">
         <is>
           <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92472245</t>
         </is>
       </c>
     </row>
@@ -11485,6 +11995,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54749942</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11591,8 +12106,118 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65338300</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>